--- a/public/Data_Cracks and Potholes 2.xlsx
+++ b/public/Data_Cracks and Potholes 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://protivitimf-my.sharepoint.com/personal/harivardhan_r_protivitiglobal_in/Documents/Desktop/road-survey/Road-Survey/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{095D9041-6D00-48F3-B03A-5971923195BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCA78059-F457-48E8-9D10-76E102015144}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{095D9041-6D00-48F3-B03A-5971923195BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E11E9B9-B538-483F-9CA0-2591CDD29B01}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B467F67D-8F37-4A99-A002-C9E06355F6C0}"/>
   </bookViews>
@@ -282,7 +282,7 @@
     <t>Potholes</t>
   </si>
   <si>
-    <t>20220816_07_24_19_705_000_hnEYwZk1I5RsPJ0KVT40Wir0BSh1_F_4160_3120 (1).jpg</t>
+    <t>20220816_07_25_32_794_000_hnEYwZk1I5RsPJ0KVT40Wir0BSh1_F_4160_3120 (1).jpg</t>
   </si>
 </sst>
 </file>
